--- a/docs/launch-playbook.xlsx
+++ b/docs/launch-playbook.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,46 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00374151"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00111827"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00374151"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +78,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F2937"/>
         <bgColor rgb="001F2937"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -92,25 +131,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -489,573 +549,855 @@
     <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>CREATOR OUTREACH — LAUNCH PLAYBOOK</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="25" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Target: First 5-10 paying customers via Ryan's 100 warm leads. 5% = $250 MRR baseline. 10% = $500 MRR strong launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="10" customHeight="1">
+      <c r="A3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="45" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>CRITICAL PATH:  Ryan replies w/ LLC info (#8)  →  [Dylan polishes product + writes emails (#1-7)]  +  [Ryan files DBA, reviews contract, curates leads, films founder video (#9-13)]  →  Both sign agreement (#16)  →  Ryan sends warm intros (#14)  →  Dylan closes (#15)  →  Daily sync during launch (#17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="10" customHeight="1">
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>VIDEO STRATEGY — two videos, two functions, BOTH linked in the warm intro:</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="35" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>• FOUNDER STORY VIDEO (Ryan, item #13): 2-4 min. Ryan tells his story — industry experience, why this product, what it means to him — ending with the product as the resolution. Ryan is a video creator/editor; this is his lane. Sells the WHY. Builds emotional trust with cold-warm leads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="35" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>• PRODUCT DEMO VIDEO (Dylan, item #1): 3-5 min. Practical walkthrough of AI fit score, 5-platform search, outreach send, CRM, custom analytics. Sells the WHAT. Builds belief in the product itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="35" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>• ORDER IN INTRO EMAIL: founder video first (hook). 'If you want to see the product itself, here's a 5-min demo.' (link).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="10" customHeight="1">
+      <c r="A10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="25" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>OWNER COLOR CODE — Dylan = light blue,  Ryan = light yellow,  Joint = light green</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="10" customHeight="1">
+      <c r="A12" t="inlineStr"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>Why It Matters</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>Time</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="60" customHeight="1">
-      <c r="A2" s="2" t="n">
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Dylan</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Build product demo video (3-5 min)</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>Walk through AI fit score, 5-platform search, outreach send, CRM, custom analytics. Practical, not narrative. Ryan links this in warm intros so leads can see the product.</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>2-4 hrs</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-    </row>
-    <row r="3" ht="60" customHeight="1">
-      <c r="A3" s="2" t="n">
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Dylan</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Write Ryan's warm-intro email template</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>First impression for all 100 leads. Casual + credible + clear ask. Claude can draft.</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-    </row>
-    <row r="4" ht="60" customHeight="1">
-      <c r="A4" s="2" t="n">
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Dylan</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>Write follow-up email sequence (first reply + 2-3 follow-ups)</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Conversion determinant. Most leads need 2-3 touches before they bite. Claude can draft.</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="2" t="n">
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Dylan</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Set up Founders' 50 discount in Stripe</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>First 10 customers get $20/mo locked forever OR 2 months free. Urgency + reward for early adopters. Stripe coupons handle it.</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6" ht="60" customHeight="1">
-      <c r="A6" s="2" t="n">
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Dylan</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>Walk through onboarding as a new user</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Incognito → signup → first search → first outreach. Fix anything janky. First 5 minutes determines 5/10 vs 8/10 conversion.</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="2" t="n">
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Dylan</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Polish /pricing page FAQ</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Anticipate top 5 objections + answer inline. Where leads decide yes/no.</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="A8" s="2" t="n">
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Dylan</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Plan testimonial collection</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>What's the moment you ask each customer for a quote? After first successful campaign? At day 14? First 5 testimonials = next 100 customers.</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9" ht="60" customHeight="1">
-      <c r="A9" s="5" t="n">
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>Ryan</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>Reply with Gaynor Media LLC info</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
         <is>
           <t>State, county, full registered address, EIN. Unblocks DBA filing + Stripe legal-name fields + legal-doc placeholders. Critical-path first step.</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>1 min</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>Ryan</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>Review employment contract for non-compete / non-solicit</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Flag any clauses that restrict working on a side venture. Identify accounts in the 100-lead pipeline that are 'off-limits' (current employer's customers).</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>20 min</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="5" t="n">
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>Ryan</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>File DBA for 'Creator Outreach'</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Illinois SOS → LLC Assumed Name Adoption → $120 fee → 7-10 business day approval. Lets the LLC legally use 'Creator Outreach' brand. Cleans up Stripe customer statements.</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>15 min filing + 10-day wait</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12" ht="60" customHeight="1">
-      <c r="A12" s="5" t="n">
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>Ryan</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Read founders agreement draft</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>1 page in docs/founders-agreement.md. Flag any changes. Aligns on roles, revenue split (Dylan 55 / Ryan 45), sunset / cost-recovery, decision-making (50/50), Illinois governing law.</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>10 min</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="5" t="n">
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>Ryan</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Curate the 100 leads</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Segment into 'safe to intro' vs 'skip' based on contract review (#9). Build the actual list with email + context per lead. Determines who Ryan actually reaches out to.</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>30-60 min</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14" ht="60" customHeight="1">
-      <c r="A14" s="5" t="n">
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G26" s="9" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>Ryan</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>Produce founder story video (2-4 min)</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Ryan tells his story (industry experience, why this product, what it means) ending with the product as the resolution. Ryan's lane as a video creator/editor. Sells the WHY; product demo (#1) sells the WHAT. Both linked in the warm intro.</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>1-2 days (Ryan's editing time)</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="5" t="n">
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Ryan</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Send the warm intros</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Use the intro template (#2) to the curated leads (#12), batch by batch so Dylan can keep up with inbound. This is where the 5-10 first customers come from.</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>1-2 hrs across launch week</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16" ht="60" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Joint</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>Dylan follows up + closes</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Reply to interested leads, book calls if needed, send checkout link, handle questions. Dylan owns the customer-facing pipeline.</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Async, ongoing during launch</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr"/>
-    </row>
-    <row r="17" ht="60" customHeight="1">
-      <c r="A17" s="6" t="n">
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B30" s="11" t="inlineStr">
         <is>
           <t>Joint</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Both sign founders agreement</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>DocuSign / HelloSign / wet ink. Dylan files signed PDF into /admin/legal under Partner Agreements + flips status Draft → Signed.</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>5 min once both review</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18" ht="60" customHeight="1">
-      <c r="A18" s="6" t="n">
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>Joint</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>Daily 5-min sync during launch week</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>What's converting, what's not, what to tweak. Async OK (Slack / text). Real-time iteration. Most learnings happen in the first 10 leads.</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>5 min/day for ~2 weeks</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>NOTES, OPEN QUESTIONS &amp; DEFERRED ITEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="8" customHeight="1">
+      <c r="A35" t="inlineStr"/>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>VIDEO STRATEGY (re-statement for visibility):</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Ryan's founder video and Dylan's product demo serve different functions and are NOT redundant. Founder video = emotional trust-builder, 2-4 min, Ryan-produced. Demo video = practical walkthrough, 3-5 min, Dylan-produced. Both must exist before the warm-intro push. Link both in every intro email — founder video first as the hook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>DISCOUNT DESIGN (item #4) — decide before launch:</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>• Option A: $20/mo locked forever for first 10 customers (lifetime founder pricing). Strongest signal of value. Hardest to walk back later.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>• Option B: 2 months free at $50/mo. Easier to upsell. Less margin compression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>• Option C: 50% off first 6 months. Middle ground. Standard SaaS launch playbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="8" customHeight="1">
+      <c r="A43" t="inlineStr"/>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>TESTIMONIAL COLLECTION (item #7) — ideas:</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>• Founder DM after first successful outreach campaign: 'got a sec for a 1-line quote?'</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>• In-app banner asking after 14 days of use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>• During the daily sync — flag a happy customer, both founders prompt them in parallel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="8" customHeight="1">
+      <c r="A48" t="inlineStr"/>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>CONVERSION TARGETS — calibration for the 100-lead push:</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>• 5% conversion = 5 paying customers = $250 MRR = $3,000 ARR — good baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>• 10% conversion = 10 paying customers = $500 MRR = $6,000 ARR — strong launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>• 15%+ conversion — strong founder-led sales signal. Hire-decision territory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1">
+      <c r="A53" t="inlineStr"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>DEFERRED ITEMS — not blocking launch:</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>• Insurance quote (Vouch / Embroker) — $1-3K/yr, cyber + E&amp;O. Get once first customers exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>• Supabase Pro upgrade ($25/mo) — before first paying customer (daily backups).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>• Stripe trial-end reminder email toggle — 30 sec, do whenever.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>• Founder agreement signing — once both founders review the draft.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>• Namecheap LLC card swap — at next renewal (~11 months out).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="8" customHeight="1">
+      <c r="A60" t="inlineStr"/>
+    </row>
+    <row r="61" ht="25" customHeight="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>REGENERATE: edit ROWS in scripts/build-launch-playbook-xlsx.py and run `python3 scripts/build-launch-playbook-xlsx.py`</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="40">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A60:G60"/>
+    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F15:F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pending,In Progress,Done,Blocked"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/launch-playbook.xlsx
+++ b/docs/launch-playbook.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:G57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>CRITICAL PATH:  Ryan replies w/ LLC info (#8)  →  [Dylan polishes product + writes emails (#1-7)]  +  [Ryan files DBA, reviews contract, curates leads, films founder video (#9-13)]  →  Both sign agreement (#16)  →  Ryan sends warm intros (#14)  →  Dylan closes (#15)  →  Daily sync during launch (#17)</t>
+          <t>CRITICAL PATH:  Ryan replies w/ LLC info (#8)  →  [Dylan polishes product + writes emails (#1-7)]  +  [Ryan reviews contract, curates leads, films founder video (#9-11)]  →  Ryan sends warm intros (#12)  →  Dylan closes (#13)  →  Daily sync during launch (#14)</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>First impression for all 100 leads. Casual + credible + clear ask. Claude can draft.</t>
+          <t>First impression for all 100 leads. Casual + credible + clear ask.</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
-          <t>Conversion determinant. Most leads need 2-3 touches before they bite. Claude can draft.</t>
+          <t>Conversion determinant. Most leads need 2-3 touches before they bite.</t>
         </is>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Set up Founders' 50 discount in Stripe</t>
+          <t>Set up early-customer discount in Stripe</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>What's the moment you ask each customer for a quote? After first successful campaign? At day 14? First 5 testimonials = next 100 customers.</t>
+          <t>What's the moment you ask each customer for a quote? First 5 testimonials = next 100 customers.</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>State, county, full registered address, EIN. Unblocks DBA filing + Stripe legal-name fields + legal-doc placeholders. Critical-path first step.</t>
+          <t>State, county, full registered address, EIN. Unblocks Stripe legal-name fields + legal-doc placeholders.</t>
         </is>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -944,17 +944,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>File DBA for 'Creator Outreach'</t>
+          <t>Curate the 100 leads</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>Illinois SOS → LLC Assumed Name Adoption → $120 fee → 7-10 business day approval. Lets the LLC legally use 'Creator Outreach' brand. Cleans up Stripe customer statements.</t>
+          <t>Segment into 'safe to intro' vs 'skip' based on contract review (#9). Build the actual list with email + context per lead.</t>
         </is>
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>15 min filing + 10-day wait</t>
+          <t>30-60 min</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
@@ -975,17 +975,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Read founders agreement draft</t>
+          <t>Produce founder story video (2-4 min)</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>1 page in docs/founders-agreement.md. Flag any changes. Aligns on roles, revenue split (Dylan 55 / Ryan 45), sunset / cost-recovery, decision-making (50/50), Illinois governing law.</t>
+          <t>Ryan tells his story — industry experience, why this product, what it means to him — ending with the product as the resolution. Ryan's lane as a video creator/editor. Sells the WHY; product demo (#1) sells the WHAT. Both linked in the warm intro.</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1-2 days (Ryan's editing time)</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Curate the 100 leads</t>
+          <t>Send the warm intros</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Segment into 'safe to intro' vs 'skip' based on contract review (#9). Build the actual list with email + context per lead. Determines who Ryan actually reaches out to.</t>
+          <t>Use the intro template (#2) to the curated leads (#10), batch by batch so Dylan can keep up with inbound. This is where the 5-10 first customers come from.</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>30-60 min</t>
+          <t>1-2 hrs across launch week</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
@@ -1027,27 +1027,27 @@
       <c r="G26" s="9" t="inlineStr"/>
     </row>
     <row r="27" ht="60" customHeight="1">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B27" s="10" t="inlineStr">
-        <is>
-          <t>Ryan</t>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Joint</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Produce founder story video (2-4 min)</t>
+          <t>Dylan follows up + closes</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>Ryan tells his story (industry experience, why this product, what it means) ending with the product as the resolution. Ryan's lane as a video creator/editor. Sells the WHY; product demo (#1) sells the WHAT. Both linked in the warm intro.</t>
+          <t>Reply to interested leads, book calls if needed, send checkout link, handle questions.</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>1-2 days (Ryan's editing time)</t>
+          <t>Async, ongoing during launch</t>
         </is>
       </c>
       <c r="F27" s="9" t="inlineStr">
@@ -1058,27 +1058,27 @@
       <c r="G27" s="9" t="inlineStr"/>
     </row>
     <row r="28" ht="60" customHeight="1">
-      <c r="A28" s="10" t="n">
+      <c r="A28" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="B28" s="10" t="inlineStr">
-        <is>
-          <t>Ryan</t>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Joint</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Send the warm intros</t>
+          <t>Daily 5-min sync during launch week</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>Use the intro template (#2) to the curated leads (#12), batch by batch so Dylan can keep up with inbound. This is where the 5-10 first customers come from.</t>
+          <t>What's converting, what's not, what to tweak. Async OK (Slack / text). Most learnings happen in the first 10 leads.</t>
         </is>
       </c>
       <c r="E28" s="9" t="inlineStr">
         <is>
-          <t>1-2 hrs across launch week</t>
+          <t>5 min/day for ~2 weeks</t>
         </is>
       </c>
       <c r="F28" s="9" t="inlineStr">
@@ -1088,103 +1088,27 @@
       </c>
       <c r="G28" s="9" t="inlineStr"/>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="B29" s="11" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Dylan follows up + closes</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Reply to interested leads, book calls if needed, send checkout link, handle questions. Dylan owns the customer-facing pipeline.</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Async, ongoing during launch</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr"/>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="B30" s="11" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>Both sign founders agreement</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>DocuSign / HelloSign / wet ink. Dylan files signed PDF into /admin/legal under Partner Agreements + flips status Draft → Signed.</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>5 min once both review</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G30" s="9" t="inlineStr"/>
-    </row>
-    <row r="31" ht="60" customHeight="1">
-      <c r="A31" s="11" t="n">
-        <v>17</v>
-      </c>
-      <c r="B31" s="11" t="inlineStr">
-        <is>
-          <t>Joint</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Daily 5-min sync during launch week</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>What's converting, what's not, what to tweak. Async OK (Slack / text). Real-time iteration. Most learnings happen in the first 10 leads.</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>5 min/day for ~2 weeks</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr"/>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>NOTES, OPEN QUESTIONS &amp; DEFERRED ITEMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="8" customHeight="1">
+      <c r="A32" t="inlineStr"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>VIDEO STRATEGY (re-statement for visibility):</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>NOTES, OPEN QUESTIONS &amp; DEFERRED ITEMS</t>
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Ryan's founder video and Dylan's product demo serve different functions and are NOT redundant. Founder video = emotional trust-builder, 2-4 min, Ryan-produced. Demo video = practical walkthrough, 3-5 min, Dylan-produced. Both must exist before the warm-intro push. Link both in every intro email — founder video first as the hook.</t>
         </is>
       </c>
     </row>
@@ -1194,167 +1118,144 @@
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>VIDEO STRATEGY (re-statement for visibility):</t>
+          <t>DISCOUNT DESIGN (item #4) — decide before launch:</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>Ryan's founder video and Dylan's product demo serve different functions and are NOT redundant. Founder video = emotional trust-builder, 2-4 min, Ryan-produced. Demo video = practical walkthrough, 3-5 min, Dylan-produced. Both must exist before the warm-intro push. Link both in every intro email — founder video first as the hook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="8" customHeight="1">
-      <c r="A38" t="inlineStr"/>
-    </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>DISCOUNT DESIGN (item #4) — decide before launch:</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
           <t>• Option A: $20/mo locked forever for first 10 customers (lifetime founder pricing). Strongest signal of value. Hardest to walk back later.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>• Option B: 2 months free at $50/mo. Easier to upsell. Less margin compression.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>• Option C: 50% off first 6 months. Middle ground. Standard SaaS launch playbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="8" customHeight="1">
+      <c r="A40" t="inlineStr"/>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>TESTIMONIAL COLLECTION (item #7) — ideas:</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>• Option C: 50% off first 6 months. Middle ground. Standard SaaS launch playbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="8" customHeight="1">
-      <c r="A43" t="inlineStr"/>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>TESTIMONIAL COLLECTION (item #7) — ideas:</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
           <t>• Founder DM after first successful outreach campaign: 'got a sec for a 1-line quote?'</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>• In-app banner asking after 14 days of use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>• During the daily sync — flag a happy customer, both founders prompt them in parallel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="8" customHeight="1">
+      <c r="A45" t="inlineStr"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>CONVERSION TARGETS — calibration for the 100-lead push:</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>• During the daily sync — flag a happy customer, both founders prompt them in parallel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="8" customHeight="1">
-      <c r="A48" t="inlineStr"/>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>CONVERSION TARGETS — calibration for the 100-lead push:</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
           <t>• 5% conversion = 5 paying customers = $250 MRR = $3,000 ARR — good baseline.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>• 10% conversion = 10 paying customers = $500 MRR = $6,000 ARR — strong launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>• 15%+ conversion — strong founder-led sales signal. Hire-decision territory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="8" customHeight="1">
+      <c r="A50" t="inlineStr"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>DEFERRED ITEMS — not blocking launch:</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>• 15%+ conversion — strong founder-led sales signal. Hire-decision territory.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="8" customHeight="1">
-      <c r="A53" t="inlineStr"/>
-    </row>
-    <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>DEFERRED ITEMS — not blocking launch:</t>
+          <t>• Insurance quote (Vouch / Embroker) — $1-3K/yr, cyber + E&amp;O. Get once first customers exist.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>• Supabase Pro upgrade ($25/mo) — before first paying customer (daily backups).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>• Stripe trial-end reminder email toggle — 30 sec, do whenever.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>• Insurance quote (Vouch / Embroker) — $1-3K/yr, cyber + E&amp;O. Get once first customers exist.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>• Supabase Pro upgrade ($25/mo) — before first paying customer (daily backups).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="5" t="inlineStr">
-        <is>
-          <t>• Stripe trial-end reminder email toggle — 30 sec, do whenever.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>• Founder agreement signing — once both founders review the draft.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="5" t="inlineStr">
-        <is>
           <t>• Namecheap LLC card swap — at next renewal (~11 months out).</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="8" customHeight="1">
-      <c r="A60" t="inlineStr"/>
-    </row>
-    <row r="61" ht="25" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
+    <row r="56" ht="8" customHeight="1">
+      <c r="A56" t="inlineStr"/>
+    </row>
+    <row r="57" ht="25" customHeight="1">
+      <c r="A57" s="13" t="inlineStr">
         <is>
           <t>REGENERATE: edit ROWS in scripts/build-launch-playbook-xlsx.py and run `python3 scripts/build-launch-playbook-xlsx.py`</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="39">
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A53:G53"/>
     <mergeCell ref="A35:G35"/>
@@ -1365,20 +1266,17 @@
     <mergeCell ref="A43:G43"/>
     <mergeCell ref="A10:G10"/>
     <mergeCell ref="A44:G44"/>
-    <mergeCell ref="A58:G58"/>
     <mergeCell ref="A40:G40"/>
     <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A34:G34"/>
     <mergeCell ref="A48:G48"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A60:G60"/>
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="A49:G49"/>
     <mergeCell ref="A51:G51"/>
     <mergeCell ref="A45:G45"/>
     <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A61:G61"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A54:G54"/>
@@ -1393,11 +1291,12 @@
     <mergeCell ref="A50:G50"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="F15:F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F15:F28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pending,In Progress,Done,Blocked"</formula1>
     </dataValidation>
   </dataValidations>
